--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.1800621983609</v>
+        <v>4.091760107233647</v>
       </c>
       <c r="D2" t="n">
-        <v>10.14359458699945</v>
+        <v>1.648334120387411</v>
       </c>
       <c r="E2" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F2" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.23384763881503</v>
+        <v>3.938000241307443</v>
       </c>
       <c r="D3" t="n">
-        <v>23.80371235390698</v>
+        <v>3.868103257509885</v>
       </c>
       <c r="E3" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F3" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.02157434032801</v>
+        <v>5.203505830303301</v>
       </c>
       <c r="D4" t="n">
-        <v>25.30316185775999</v>
+        <v>4.111763801885998</v>
       </c>
       <c r="E4" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F4" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.45760471919467</v>
+        <v>2.836860766869135</v>
       </c>
       <c r="D5" t="n">
-        <v>17.1070486019009</v>
+        <v>2.779895397808896</v>
       </c>
       <c r="E5" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F5" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.53814988833747</v>
+        <v>1.224949356854839</v>
       </c>
       <c r="D6" t="n">
-        <v>6.798545737424222</v>
+        <v>1.104763682331436</v>
       </c>
       <c r="E6" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F6" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.59454513379142</v>
+        <v>3.021613584241106</v>
       </c>
       <c r="D7" t="n">
-        <v>17.85388794160953</v>
+        <v>2.901256790511548</v>
       </c>
       <c r="E7" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F7" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.80328237461775</v>
+        <v>2.568033385875385</v>
       </c>
       <c r="D8" t="n">
-        <v>15.21292857866571</v>
+        <v>2.472100894033179</v>
       </c>
       <c r="E8" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F8" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.43488809618257</v>
+        <v>7.708169315629668</v>
       </c>
       <c r="D9" t="n">
-        <v>47.45259209681428</v>
+        <v>7.711046215732321</v>
       </c>
       <c r="E9" t="n">
-        <v>11.31062928807377</v>
+        <v>1.837977259311988</v>
       </c>
       <c r="F9" t="n">
-        <v>11.7359813686443</v>
+        <v>1.907096972404699</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
